--- a/data.mn/public/datasets/mrpam-commodity-prices.xlsx
+++ b/data.mn/public/datasets/mrpam-commodity-prices.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3973,6 +3973,110 @@
         <v>3595.53</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>14352.45</v>
+      </c>
+      <c r="C69" t="n">
+        <v>520</v>
+      </c>
+      <c r="D69" t="n">
+        <v>425</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4402.01</v>
+      </c>
+      <c r="F69" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="G69" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1854.41</v>
+      </c>
+      <c r="I69" t="n">
+        <v>180.17</v>
+      </c>
+      <c r="J69" t="n">
+        <v>73475.58</v>
+      </c>
+      <c r="K69" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="L69" t="n">
+        <v>55633.13</v>
+      </c>
+      <c r="M69" t="n">
+        <v>60766.9</v>
+      </c>
+      <c r="N69" t="n">
+        <v>199047.62</v>
+      </c>
+      <c r="O69" t="n">
+        <v>197.71</v>
+      </c>
+      <c r="P69" t="n">
+        <v>3874.48</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>14482.73</v>
+      </c>
+      <c r="C70" t="n">
+        <v>520</v>
+      </c>
+      <c r="D70" t="n">
+        <v>425</v>
+      </c>
+      <c r="E70" t="n">
+        <v>4335.65</v>
+      </c>
+      <c r="F70" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="G70" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1870.44</v>
+      </c>
+      <c r="I70" t="n">
+        <v>182.97</v>
+      </c>
+      <c r="J70" t="n">
+        <v>74031.14</v>
+      </c>
+      <c r="K70" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="L70" t="n">
+        <v>53861.36</v>
+      </c>
+      <c r="M70" t="n">
+        <v>60408.36</v>
+      </c>
+      <c r="N70" t="n">
+        <v>189210.53</v>
+      </c>
+      <c r="O70" t="n">
+        <v>197.6</v>
+      </c>
+      <c r="P70" t="n">
+        <v>4018.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3984,7 +4088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7543,6 +7647,110 @@
         <v>3595.53</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>4402.01</v>
+      </c>
+      <c r="C69" t="n">
+        <v>60766.9</v>
+      </c>
+      <c r="D69" t="n">
+        <v>199047.62</v>
+      </c>
+      <c r="E69" t="n">
+        <v>520</v>
+      </c>
+      <c r="F69" t="n">
+        <v>425</v>
+      </c>
+      <c r="G69" t="n">
+        <v>14352.45</v>
+      </c>
+      <c r="H69" t="n">
+        <v>180.17</v>
+      </c>
+      <c r="I69" t="n">
+        <v>73475.58</v>
+      </c>
+      <c r="J69" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="K69" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="L69" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="M69" t="n">
+        <v>197.71</v>
+      </c>
+      <c r="N69" t="n">
+        <v>1854.41</v>
+      </c>
+      <c r="O69" t="n">
+        <v>55633.13</v>
+      </c>
+      <c r="P69" t="n">
+        <v>3874.48</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>4335.65</v>
+      </c>
+      <c r="C70" t="n">
+        <v>60408.36</v>
+      </c>
+      <c r="D70" t="n">
+        <v>189210.53</v>
+      </c>
+      <c r="E70" t="n">
+        <v>520</v>
+      </c>
+      <c r="F70" t="n">
+        <v>425</v>
+      </c>
+      <c r="G70" t="n">
+        <v>14482.73</v>
+      </c>
+      <c r="H70" t="n">
+        <v>182.97</v>
+      </c>
+      <c r="I70" t="n">
+        <v>74031.14</v>
+      </c>
+      <c r="J70" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="K70" t="n">
+        <v>52.93</v>
+      </c>
+      <c r="L70" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="M70" t="n">
+        <v>197.6</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1870.44</v>
+      </c>
+      <c r="O70" t="n">
+        <v>53861.36</v>
+      </c>
+      <c r="P70" t="n">
+        <v>4018.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
